--- a/144F20/Topic 2/Topic2DQ1Template.xlsx
+++ b/144F20/Topic 2/Topic2DQ1Template.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144F20/Topic 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.ketchersid\tmp\ugh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:80_{EDBBA819-AFBE-4435-A3A7-9D5A2321AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B058A6-8A9D-4647-8080-24E3C5929DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="915" windowWidth="25995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Percents" sheetId="1" r:id="rId1"/>
-    <sheet name="Solution" sheetId="3" state="hidden" r:id="rId2"/>
-    <sheet name="Random" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Users" sheetId="5" state="hidden" r:id="rId2"/>
+    <sheet name="Solution" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Random" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <customWorkbookViews>
-    <customWorkbookView name="Richard Ketchersid - Personal View" guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" mergeInterval="0" personalView="1" xWindow="61" yWindow="61" windowWidth="1733" windowHeight="952" activeSheetId="1"/>
+    <customWorkbookView name="Richard Ketchersid - Personal View" guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" mergeInterval="0" personalView="1" xWindow="61" yWindow="61" windowWidth="1733" windowHeight="952" activeSheetId="5"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>Enter your name (at least 5 letters)</t>
+  </si>
+  <si>
+    <t>Your Name</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
   <si>
     <t>Original Amount</t>
   </si>
@@ -56,121 +66,43 @@
     <t>% Change (percent form)</t>
   </si>
   <si>
-    <t>Legend</t>
-  </si>
-  <si>
     <t>If a cell is shaded</t>
   </si>
   <si>
+    <t>Cell Should Contain</t>
+  </si>
+  <si>
     <t>Blue</t>
   </si>
   <si>
+    <t>Text</t>
+  </si>
+  <si>
     <t>Green</t>
   </si>
   <si>
+    <t>Number</t>
+  </si>
+  <si>
     <t>Gold</t>
   </si>
   <si>
+    <t>Excel Formula</t>
+  </si>
+  <si>
     <t>Any other color</t>
   </si>
   <si>
     <t>Make no changes</t>
   </si>
   <si>
-    <t>Cell Should Contain</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Excel Formula</t>
-  </si>
-  <si>
-    <t>Enter your name (at least 5 letters)</t>
-  </si>
-  <si>
-    <t>Seed</t>
-  </si>
-  <si>
-    <t>Rand1</t>
-  </si>
-  <si>
-    <t>Rand2</t>
-  </si>
-  <si>
-    <t>Rand3</t>
-  </si>
-  <si>
-    <t>Rand4</t>
-  </si>
-  <si>
-    <t>Rand5</t>
-  </si>
-  <si>
-    <t>Rand6</t>
-  </si>
-  <si>
-    <t>Rand7</t>
-  </si>
-  <si>
-    <t>Rand8</t>
-  </si>
-  <si>
-    <t>Rand9</t>
-  </si>
-  <si>
-    <t>Rand10</t>
-  </si>
-  <si>
-    <t>Rand11</t>
-  </si>
-  <si>
-    <t>Rand12</t>
-  </si>
-  <si>
-    <t>Rand13</t>
-  </si>
-  <si>
-    <t>Rand14</t>
-  </si>
-  <si>
-    <t>Rand15</t>
-  </si>
-  <si>
-    <t>Rand16</t>
-  </si>
-  <si>
-    <t>Rand17</t>
-  </si>
-  <si>
-    <t>Rand18</t>
-  </si>
-  <si>
-    <t>Rand19</t>
-  </si>
-  <si>
-    <t>Rand20</t>
-  </si>
-  <si>
-    <t>Rand21</t>
-  </si>
-  <si>
-    <t>Rand22</t>
-  </si>
-  <si>
-    <t>Your Name</t>
+    <t>Show two decimals</t>
   </si>
   <si>
     <t>Show four decimal places</t>
   </si>
   <si>
     <t>Show two decimal places</t>
-  </si>
-  <si>
-    <t>Show two decimals</t>
   </si>
   <si>
     <r>
@@ -218,6 +150,81 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Seed</t>
+  </si>
+  <si>
+    <t>Rand1</t>
+  </si>
+  <si>
+    <t>Rand2</t>
+  </si>
+  <si>
+    <t>Rand3</t>
+  </si>
+  <si>
+    <t>Rand4</t>
+  </si>
+  <si>
+    <t>Rand5</t>
+  </si>
+  <si>
+    <t>Rand6</t>
+  </si>
+  <si>
+    <t>Rand7</t>
+  </si>
+  <si>
+    <t>Rand8</t>
+  </si>
+  <si>
+    <t>Rand9</t>
+  </si>
+  <si>
+    <t>Rand10</t>
+  </si>
+  <si>
+    <t>Rand11</t>
+  </si>
+  <si>
+    <t>Rand12</t>
+  </si>
+  <si>
+    <t>Rand13</t>
+  </si>
+  <si>
+    <t>Rand14</t>
+  </si>
+  <si>
+    <t>Rand15</t>
+  </si>
+  <si>
+    <t>Rand16</t>
+  </si>
+  <si>
+    <t>Rand17</t>
+  </si>
+  <si>
+    <t>Rand18</t>
+  </si>
+  <si>
+    <t>Rand19</t>
+  </si>
+  <si>
+    <t>Rand20</t>
+  </si>
+  <si>
+    <t>Rand21</t>
+  </si>
+  <si>
+    <t>Rand22</t>
   </si>
   <si>
     <t>Ignore the Halo preview you must download and open the file in Excel to correctly see the contents.</t>
@@ -652,7 +659,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -710,12 +717,16 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -750,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -767,6 +778,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -888,6 +903,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0" tint="-0.14996795556505021"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <color rgb="FF00B050"/>
@@ -918,25 +943,15 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FF00B050"/>
+        <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -949,45 +964,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{1689A0DF-255D-4085-B2FB-E10FA6E69055}" diskRevisions="1" version="2">
-  <header guid="{5C423E65-871E-4286-ACD0-3800CFF68550}" dateTime="2022-07-20T13:48:49" maxSheetId="5" userName="Richard Ketchersid" r:id="rId1">
-    <sheetIdMap count="4">
-      <sheetId val="1"/>
-      <sheetId val="2"/>
-      <sheetId val="3"/>
-      <sheetId val="4"/>
-    </sheetIdMap>
-  </header>
-  <header guid="{1689A0DF-255D-4085-B2FB-E10FA6E69055}" dateTime="2022-07-20T14:39:24" maxSheetId="5" userName="Richard Ketchersid" r:id="rId2">
-    <sheetIdMap count="4">
-      <sheetId val="1"/>
-      <sheetId val="3"/>
-      <sheetId val="4"/>
-      <sheetId val="2"/>
-    </sheetIdMap>
-  </header>
-</headers>
-</file>
-
-<file path=xl/revisions/revisionLog1.xml><?xml version="1.0" encoding="utf-8"?>
-<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac"/>
-</file>
-
-<file path=xl/revisions/revisionLog2.xml><?xml version="1.0" encoding="utf-8"?>
-<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <rcv guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" action="delete"/>
-  <rcv guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" action="add"/>
-</revisions>
-</file>
-
-<file path=xl/revisions/userNames.xml><?xml version="1.0" encoding="utf-8"?>
-<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="2">
-  <userInfo guid="{5C423E65-871E-4286-ACD0-3800CFF68550}" name="Richard Ketchersid" id="-1739556272" dateTime="2022-07-20T13:48:49"/>
-  <userInfo guid="{1689A0DF-255D-4085-B2FB-E10FA6E69055}" name="Richard Ketchersid" id="-1739564910" dateTime="2022-07-20T14:38:56"/>
-</users>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1261,48 +1237,47 @@
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A2" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="28" t="s">
-        <v>40</v>
+      <c r="A2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="46" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" thickTop="1" thickBot="1">
-      <c r="G3" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="30"/>
+      <c r="G3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="31"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="18" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1318,10 +1293,10 @@
       <c r="D5" s="27"/>
       <c r="E5" s="22"/>
       <c r="G5" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1337,10 +1312,10 @@
       <c r="D6" s="17"/>
       <c r="E6" s="22"/>
       <c r="G6" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1356,7 +1331,7 @@
       <c r="D7" s="17"/>
       <c r="E7" s="22"/>
       <c r="G7" s="7" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>15</v>
@@ -1375,10 +1350,10 @@
       <c r="D8" s="17"/>
       <c r="E8" s="22"/>
       <c r="G8" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickTop="1">
@@ -1434,45 +1409,45 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A13" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="A13" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="15" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B15" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
+      <c r="B15" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1">
-      <c r="B17" s="41"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="44"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cDBi4K1q9fUFb7oIRgVnAbOmZJZBw7TO+Ax1OqphCANkkk0O3CieOElvYP4QYXJeLyVZ0b/1zwiwysDdmx25zA==" saltValue="hGHcc6ftYXI2QgQtid9zcg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="U0Hj7rcGQzO6SMgufXBqUODQuC3ww8tXpNHmQPnlIu1ZNf042wi6cpwfRVVwRV+QpZfH66CMvoqt2r4ALo+oYQ==" saltValue="kPRczeKeIFxbHdV19T2U4g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
   <customSheetViews>
     <customSheetView guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}">
       <selection activeCell="H16" sqref="H16"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
@@ -1483,7 +1458,7 @@
     <mergeCell ref="B15:E17"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:E12">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>$D$2="Your Name"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1493,6 +1468,16 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="44" id="{5F8CF386-A089-4D42-9F11-FDD5F2503D44}">
+            <xm:f>OR(NOT(_xlfn.ISFORMULA(A7)),ABS(A7-Solution!A7)&gt;0.00005)</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="expression" priority="56" id="{E9611DED-43D1-4477-97E6-AED09D5C24E8}">
             <xm:f>AND(_xlfn.ISFORMULA(A7),ABS(A7-Solution!A7)&lt;0.0005)</xm:f>
             <x14:dxf>
@@ -1500,16 +1485,6 @@
                 <b/>
                 <i val="0"/>
                 <color rgb="FF00B050"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="44" id="{5F8CF386-A089-4D42-9F11-FDD5F2503D44}">
-            <xm:f>OR(NOT(_xlfn.ISFORMULA(A7)),ABS(A7-Solution!A7)&gt;0.00005)</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
               </font>
             </x14:dxf>
           </x14:cfRule>
@@ -1631,6 +1606,29 @@
           <xm:sqref>B12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="8" id="{1D43F37E-8E51-486D-92C5-27AA9DA152FD}">
+            <xm:f>OR(NOT(_xlfn.ISFORMULA(C5)),ABS(C5-Solution!C5)&gt;0.00005)</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="9" id="{9B74A47D-16BC-4AB0-BE1C-358D3A1174DF}">
+            <xm:f>AND(_xlfn.ISFORMULA(C5),ABS(C5-Solution!C5)&lt;0.0005)</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FF00B050"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C5:C6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="10" id="{953AC69A-F4AF-43F2-AE36-6E7095FA1E64}">
             <xm:f>OR(NOT(_xlfn.ISFORMULA(C9)),ABS(C9-Solution!C9)&gt;0.00005)</xm:f>
             <x14:dxf>
@@ -1652,29 +1650,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>C9:C12</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="8" id="{1D43F37E-8E51-486D-92C5-27AA9DA152FD}">
-            <xm:f>OR(NOT(_xlfn.ISFORMULA(C5)),ABS(C5-Solution!C5)&gt;0.00005)</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="9" id="{9B74A47D-16BC-4AB0-BE1C-358D3A1174DF}">
-            <xm:f>AND(_xlfn.ISFORMULA(C5),ABS(C5-Solution!C5)&lt;0.0005)</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FF00B050"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C5:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="6" id="{F9AA9CCE-0BC9-4ED8-AC6D-E232A8CECC7C}">
@@ -1752,6 +1727,169 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9154A0A1-037B-4E71-95B8-1C220E537657}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" style="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="29">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Percents!D2</f>
+        <v>Your Name</v>
+      </c>
+      <c r="F1" s="28" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="M1" s="28" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="28" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="28" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Richard</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="28" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v>Richard</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="28" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="j/VeCMZPJsV8tYjBUcBmPiTzsnrmF0DVMXK4rVaZ1aEI+r8tlKbkAwNrYFp9GapIT5jxA7PXvavDi0J2m+/DCg==" saltValue="SIeF0xDMBeDeTV+DXftW3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <customSheetViews>
+    <customSheetView guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}">
+      <selection activeCell="F7" sqref="F7"/>
+      <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+    </customSheetView>
+  </customSheetViews>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A45589-C87D-4057-852E-A6F32C73CC26}">
   <dimension ref="A4:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1965,14 +2103,14 @@
   <customSheetViews>
     <customSheetView guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" state="hidden">
       <selection activeCell="H9" sqref="H9"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E43F2B4-801D-47B0-8D9E-A7895490B85A}">
   <dimension ref="A1:W45"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2604,7 +2742,7 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <f ca="1">MOD(PRODUCT(E6:E10),F13)</f>
@@ -2667,7 +2805,7 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <f ca="1">MOD(B11*F11+F12,F13)</f>
@@ -2742,7 +2880,7 @@
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B13" s="10">
         <f t="shared" ref="B13:B33" ca="1" si="3">MOD(B12*F$11+F$12,F$13)</f>
@@ -2817,7 +2955,7 @@
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B14" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -2889,7 +3027,7 @@
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B15" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -2961,7 +3099,7 @@
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B16" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3033,7 +3171,7 @@
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B17" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3105,7 +3243,7 @@
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B18" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3126,7 +3264,7 @@
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B19" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3147,7 +3285,7 @@
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B20" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3168,7 +3306,7 @@
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B21" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3189,7 +3327,7 @@
     </row>
     <row r="22" spans="1:23">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B22" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3211,7 +3349,7 @@
     </row>
     <row r="23" spans="1:23">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B23" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3233,7 +3371,7 @@
     </row>
     <row r="24" spans="1:23">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B24" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3255,7 +3393,7 @@
     </row>
     <row r="25" spans="1:23">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B25" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3277,7 +3415,7 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B26" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3299,7 +3437,7 @@
     </row>
     <row r="27" spans="1:23">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B27" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3321,7 +3459,7 @@
     </row>
     <row r="28" spans="1:23">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B28" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3343,7 +3481,7 @@
     </row>
     <row r="29" spans="1:23">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B29" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3365,7 +3503,7 @@
     </row>
     <row r="30" spans="1:23">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B30" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3387,7 +3525,7 @@
     </row>
     <row r="31" spans="1:23">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B31" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3409,7 +3547,7 @@
     </row>
     <row r="32" spans="1:23">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B32" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3431,7 +3569,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B33" s="10">
         <f t="shared" ca="1" si="3"/>
@@ -3488,84 +3626,85 @@
       <c r="M45" s="10"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Xv4bzWOe7EMom1NeXHy8I/xoSW3NFMHPF5RrKqlOX955qpdpyUTtb1VPlMC5iNjs/ZaoaVtfwxhBgQM/1aM6iw==" saltValue="tf1HZj8cbYS9Kb2OhLg0lQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <customSheetViews>
     <customSheetView guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" state="hidden" topLeftCell="A19">
       <selection activeCell="D29" sqref="D29"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8147CBD-156A-4F0A-BF12-881DFBEF92E3}">
   <dimension ref="C5:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="3:8">
-      <c r="C5" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
+      <c r="C5" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="3:8">
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
     </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{E42251D7-B26D-493B-AB47-FC9D5E718532}" state="hidden">
       <selection activeCell="C5" sqref="C5:H11"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>

--- a/144F20/Topic 2/Topic2DQ1Template.xlsx
+++ b/144F20/Topic 2/Topic2DQ1Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.ketchersid\tmp\ugh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144F20/Topic 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B058A6-8A9D-4647-8080-24E3C5929DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Percents" sheetId="1" r:id="rId1"/>
@@ -729,6 +729,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -778,10 +782,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1242,20 +1242,20 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="46" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" thickTop="1" thickBot="1">
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="31"/>
+      <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="18" t="s">
@@ -1409,11 +1409,11 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="25" t="s">
         <v>19</v>
       </c>
@@ -1423,24 +1423,24 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="15" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="39"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1">
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="44"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="U0Hj7rcGQzO6SMgufXBqUODQuC3ww8tXpNHmQPnlIu1ZNf042wi6cpwfRVVwRV+QpZfH66CMvoqt2r4ALo+oYQ==" saltValue="kPRczeKeIFxbHdV19T2U4g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
@@ -1844,19 +1844,19 @@
     <row r="16" spans="1:13">
       <c r="A16" s="28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Richard</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Richard</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Richard</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3643,62 +3643,62 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="3:8">
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="3:8">
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
     </row>
   </sheetData>
   <customSheetViews>
